--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/VALVULA - 28_01 M.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/VALVULA - 28_01 M.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,17 +507,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7898558333786</t>
+          <t>7898924047231</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE WGK CBX250 TWISTER/ CB300/ XRE300 10111411</t>
+          <t>VALVULA ADMISSAO WGK BIZ110I/ POP110I 10117311</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -528,17 +528,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7898924047231</t>
+          <t>7895797890797</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO WGK BIZ110I/ POP110I 10117311</t>
+          <t>VALVULA ADMISSAO VINI YS150 FAZER 2014/ XTZ150 2014 2020890079</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -549,17 +549,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7899641818944</t>
+          <t>7899641863456</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE VEDAMOTORS FAN125 2009/ NXR125</t>
+          <t>VALVULA ADMISSAO VEDAMOTORS CG TITAN FAN160 2015/ NX160 2016 210020</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -570,17 +570,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7895797890797</t>
+          <t>7899641818937</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VINI YS150 FAZER 2014/ XTZ150 2014 2020890079</t>
+          <t>VALVULA ADMISSAO VEDAMOTORS CG FAN125 2009/ NXR125 2009 210017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -591,17 +591,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7898558339948</t>
+          <t>7898558336848</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE WGK CB250F TWISTER 2016 EM DIANTE 10117501</t>
+          <t>VALVULA ADMISSAO WGK YS150 FAZER 10114061</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -612,17 +612,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7899641863456</t>
+          <t>7899641810658</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VEDAMOTORS CG TITAN FAN160 2015/ NX160 2016 210020</t>
+          <t>VALVULA ESCAPE VEDAMOTORS TITAN CG FAN150 2004 A 2008/ CRF150F 2012 210012</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -633,20 +633,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7899641810641</t>
+          <t>602883762633</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE VEDAMOTORS TITAN CG FAN150 2009 210011</t>
+          <t>VALVULA ADMISSAO IRON CBX250 TWISTER/ XR250/ TORNADO 185460</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -654,17 +658,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7899641818937</t>
+          <t>602883764828</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VEDAMOTORS CG FAN125 2009/ NXR125 2009 210017</t>
+          <t>VALVULA ADMISSAO IRON FAZER250 187691</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -675,20 +679,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7898558336848</t>
+          <t>7895797890841</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO WGK YS150 FAZER 10114061</t>
+          <t>VALVULA ESCAPE VINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -696,20 +704,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7898558336855</t>
+          <t>7899641879723</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE WGK YS150 FAZER 10114071</t>
+          <t>VALVULA ADMISSAO VEDAMOTORS   PCX150 2013/ SH150I 2017 210024</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -717,20 +729,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7899641810658</t>
+          <t>7898558339603</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE VEDAMOTORS TITAN CG FAN150 2004 A 2008/ CRF150F 2012 210012</t>
+          <t>VALVULA ESCAPE WGK CG125 TITAN 2002 A 2008 10117177</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -738,22 +754,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>602883762640</t>
+          <t>7898558339597</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE IRON CBX250 TWISTER 185461</t>
+          <t>VALVULA ADMISSAO WGK CG125 TITAN 2002 A 2008 10117101</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -763,83 +779,75 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>602883762633</t>
+          <t>7895797890179</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO IRON CBX250 TWISTER/ XR250/ TORNADO 185460</t>
+          <t>VALVULA ADMISSAO VINI FACTOR YBR125 2000 A 2016/ XTZ125 2003 A 2015/ TTR125 2008 E.D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>602883764828</t>
+          <t>7895797890124</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO IRON FAZER250 187691</t>
+          <t>VALVULA ESCAPEVINI CG TITAN FAN125 2003 A 2008/ BROS NXR125 2003 A 2005</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7899641873400</t>
+          <t>7899641811273</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE VEDAMOTORS PCX150 2013 210024</t>
+          <t>VALVULA ADMISSAO VEDAMOTORS CG TITAN125/ XLR125 ATE 2000 210011</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7895797890841</t>
+          <t>7895797890926</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE VINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
+          <t>VALVULA ADMISSAOVINI FACTOR YBR125 2017 E.D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -847,50 +855,46 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7895797890148</t>
+          <t>7895797890131</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALVULA ESCAPE VINI CB300R 2009 A 2015/ XRE300 2010 E.D/ CBX250 TWISTER 2001 A 2008/ XR250 TORNADO 2001 A 2008 </t>
+          <t>VALVULA ADMISSAOVINI CB300R 2009 A 2015/ XRE300 2010 E.D/ CBX250 TWISTER 2001 A 2008/ XR250 TORNADO 2001 A 2008</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7899641879723</t>
+          <t>7895797890834</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VEDAMOTORS   PCX150 2013/ SH150I 2017 210024</t>
+          <t>VALVULA ADMISSAO VINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -901,16 +905,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7898558339580</t>
+          <t>7895797890070</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE WGK CG125 TODAY 1992 A 2001 10117091</t>
+          <t>VALVULA ADMISSAO VINI C100 DREAM 1992 A 1998/ BIZ100 1998 E.D/ POP100 2007 A 2015</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -922,87 +926,71 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>7898558339603</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE WGK CG125 TITAN 2002 A 2008 10117177</t>
+          <t>VALVULA ADMISSAO CG FAN ES/KS 41025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>7898558339597</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO WGK CG125 TITAN 2002 A 2008 10117101</t>
+          <t>VALVULA ADMISSAO CG TITAN KS 2003</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7895797890179</t>
+          <t>0197894766562454304</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VINI FACTOR YBR125 2000 A 2016/ XTZ125 2003 A 2015/ TTR125 2008 E.D</t>
+          <t>VALVULA ADMISSAO MAHLE CB TWISTER250cc FLEX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7895797890087</t>
+          <t>0197892415557264304</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE VINI C100 DREAM 1992 A 1998/ BIZ100 1998 E.D/ POP100 2007 A 2015</t>
+          <t>VALVULA ADMISSAO MAHLE CG TITAN FAN125 2002 A 2004</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1010,20 +998,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7895797890186</t>
+          <t>0197892415478873304</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPE VINI FACTOR YBR125 2000 A 2016/ XTZ125 2003 A 2015/ TTR125 2008 E.D</t>
+          <t>VALVULA ADMISSAO MAHLE TWISTER/ TORNADO/ CB300R/ BROS NXR300/ XRE300</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1031,20 +1023,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7895797890124</t>
+          <t>0197892415973965304</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPEVINI CG TITAN FAN125 2003 A 2008/ BROS NXR125 2003 A 2005</t>
+          <t>VALVULA ADMISSAO MAHLE CG125 INJECAO ELETRONICA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1053,463 +1049,6 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7899641811273</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO VEDAMOTORS CG TITAN125/ XLR125 ATE 2000 210011</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7895797890926</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAOVINI FACTOR YBR125 2017 E.D</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>7893986549280</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPE PECA+ BROS NXR150</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>7895797890131</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAOVINI CB300R 2009 A 2015/ XRE300 2010 E.D/ CBX250 TWISTER 2001 A 2008/ XR250 TORNADO 2001 A 2008</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>7895797890803</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPEVINI FAZER YS150 2014 E.D/ XTZ150 CROSSER E.D</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>7895797890834</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAOVINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>7895797890070</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO VINI C100 DREAM 1992 A 1998/ BIZ100 1998 E.D/ POP100 2007 A 2015</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPE BIZ/ DREAM/ POP100cc 41018</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO CG FAN ES/KS 41025</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO CG TITAN KS 2003</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>0197894766562454304</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO MAHLE CB TWISTER250cc FLEX</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>0197892415557264304</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO MAHLE CG TITAN FAN125 2002 A 2004</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>0197892415557271304</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO MAHLE TITAN150cc 2004</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>0197894766665605304</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPE MAHLE FAZER250cc GASOLINA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>0197892415557394304</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPE MAHLE TITAN150cc 2004</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>0197892415478873304</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO MAHLE TWISTER/ TORNADO/ CB300R/ BROS NXR300/ XRE300</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>0197892415973965304</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO MAHLE CG125 INJECAO ELETRONICA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0197892415974092304</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPE MAHLE CG125 INJECAO ELETRONICA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>0197892415478644304</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPE MAHLE TWISTER/ TORNADO/ CB300R/ BROS NXR300/ XRE300</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>0197892415557417304</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VALVULA ESCAPE MAHLE YBR125cc </t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>0197894766665520304</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>VALVULA ESCAPE MAHLE FAZER250cc FLEX</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/VALVULA - 28_01 M.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/VALVULA - 28_01 M.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VEDAMOTORS NXR125 2992 A 2008/ CG125 21008</t>
+          <t>VALVULA ADMISSAO VEDAMOTORS BROS NXR125 1992 A 2008/ CG125 21008</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,7 +572,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -604,7 +592,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +612,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,11 +632,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -671,7 +652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -692,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -717,11 +692,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -742,11 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -767,11 +732,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -792,20 +752,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7895797890124</t>
+          <t>7899641811273</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VALVULA ESCAPEVINI CG TITAN FAN125 2003 A 2008/ BROS NXR125 2003 A 2005</t>
+          <t>VALVULA ADMISSAO VEDAMOTORS CG TITAN125/ XLR125 ATE 2000 210011</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -813,20 +772,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7899641811273</t>
+          <t>7895797890926</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VEDAMOTORS CG TITAN125/ XLR125 ATE 2000 210011</t>
+          <t>VALVULA ADMISSAO VINI FACTOR YBR125 2017 E.D</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -834,20 +792,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7895797890926</t>
+          <t>7895797890131</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAOVINI FACTOR YBR125 2017 E.D</t>
+          <t>VALVULA ADMISSAO VINI CB300R 2009 A 2015/ XRE300 2010 E.D/ CBX250 TWISTER 2001 A 2008/ XR250 TORNADO 2001 A 2008</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -855,20 +812,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7895797890131</t>
+          <t>7895797890834</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAOVINI CB300R 2009 A 2015/ XRE300 2010 E.D/ CBX250 TWISTER 2001 A 2008/ XR250 TORNADO 2001 A 2008</t>
+          <t>VALVULA ADMISSAO VINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -876,45 +832,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7895797890834</t>
+          <t>7895797890070</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VINI CG TITAN FAN START160 2016/ BROS NXR160 2016</t>
+          <t>VALVULA ADMISSAO VINI C100 DREAM 1992 A 1998/ BIZ100 1998 E.D/ POP100 2007 A 2015</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>7895797890070</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO VINI C100 DREAM 1992 A 1998/ BIZ100 1998 E.D/ POP100 2007 A 2015</t>
+          <t>VALVULA ADMISSAO CG FAN ES/KS 41025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -922,16 +868,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO CG FAN ES/KS 41025</t>
+          <t>VALVULA ADMISSAO CG TITAN KS 2003</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -939,16 +884,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0197894766562454304</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO CG TITAN KS 2003</t>
+          <t>VALVULA ADMISSAO MAHLE CB TWISTER250cc FLEX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -956,20 +904,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0197894766562454304</t>
+          <t>0197892415557264304</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO MAHLE CB TWISTER250cc FLEX</t>
+          <t>VALVULA ADMISSAO MAHLE CG TITAN FAN125 2002 A 2004</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -977,45 +924,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0197892415557264304</t>
+          <t>0197892415478873304</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO MAHLE CG TITAN FAN125 2002 A 2004</t>
+          <t>VALVULA ADMISSAO MAHLE TWISTER/ TORNADO/ CB300R/ BROS NXR300/ XRE300</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0197892415478873304</t>
+          <t>0197892415973965304</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VALVULA ADMISSAO MAHLE TWISTER/ TORNADO/ CB300R/ BROS NXR300/ XRE300</t>
+          <t>VALVULA ADMISSAO MAHLE CG125 INJECAO ELETRONICA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1023,32 +964,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0197892415973965304</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>VALVULA ADMISSAO MAHLE CG125 INJECAO ELETRONICA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
